--- a/data/trans_orig/Q5401-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5401-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2007</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15760</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53662</t>
+          <t>53959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22372</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56041</t>
+          <t>55178</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73602</t>
+          <t>72871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46951</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>59950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>853</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20162</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25009</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47994</t>
+          <t>48515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62050</t>
+          <t>62600</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12672</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21270</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65380</t>
+          <t>65427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>81485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,85%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29191</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33245</t>
+          <t>32969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>34265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57039</t>
+          <t>58468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>26102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50208</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77784</t>
+          <t>78281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181673</t>
+          <t>181209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>207950</t>
+          <t>207744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55968</t>
+          <t>56520</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72223</t>
+          <t>71416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>244307</t>
+          <t>242565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274358</t>
+          <t>272475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22103</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>16538</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32317</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43239</t>
+          <t>43242</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>35421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>47736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52627</t>
+          <t>53231</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72827</t>
+          <t>72936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>92141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115676</t>
+          <t>116653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,89%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41052</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>18962</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41943</t>
+          <t>41879</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81372</t>
+          <t>82265</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117631</t>
+          <t>118878</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84002</t>
+          <t>82820</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>119557</t>
+          <t>119431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>277269</t>
+          <t>277456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>316060</t>
+          <t>314384</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279189</t>
+          <t>278544</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>317411</t>
+          <t>318549</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20720</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40826</t>
+          <t>39864</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63710</t>
+          <t>62961</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95675</t>
+          <t>97896</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>68810</t>
+          <t>69257</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>99827</t>
+          <t>104762</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>135020</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>179946</t>
+          <t>182362</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>217371</t>
+          <t>216944</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>272369</t>
+          <t>268954</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>369781</t>
+          <t>365623</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>404397</t>
+          <t>403986</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>444617</t>
+          <t>442243</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>494833</t>
+          <t>492768</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>825224</t>
+          <t>825963</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>887247</t>
+          <t>885411</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2012</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40774</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50194</t>
+          <t>50384</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63883</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>43381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56538</t>
+          <t>56409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51748</t>
+          <t>50614</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68346</t>
+          <t>68870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22523</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16535</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>40160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83576</t>
+          <t>82771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103762</t>
+          <t>102946</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>31200</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43851</t>
+          <t>44152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117722</t>
+          <t>118838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143357</t>
+          <t>142970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42127</t>
+          <t>40990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>22838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>48268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26661</t>
+          <t>25305</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49215</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>24090</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>40148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67742</t>
+          <t>66386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>150443</t>
+          <t>153401</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180286</t>
+          <t>181538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46888</t>
+          <t>47006</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189595</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>220310</t>
+          <t>221440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42791</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>31672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56225</t>
+          <t>57819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>27431</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33380</t>
+          <t>33858</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>55736</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49231</t>
+          <t>49926</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77956</t>
+          <t>77521</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>61565</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79458</t>
+          <t>79980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100370</t>
+          <t>100520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127178</t>
+          <t>126823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>168859</t>
+          <t>165873</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>201018</t>
+          <t>200323</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66786</t>
+          <t>64682</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>37190</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65231</t>
+          <t>65362</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59897</t>
+          <t>58481</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90616</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59802</t>
+          <t>61700</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93288</t>
+          <t>91899</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>251286</t>
+          <t>249215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>288827</t>
+          <t>288731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>249524</t>
+          <t>253125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288781</t>
+          <t>290692</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>70021</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>77517</t>
+          <t>78748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>115846</t>
+          <t>115536</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127865</t>
+          <t>127310</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>177843</t>
+          <t>178482</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67618</t>
+          <t>66302</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104614</t>
+          <t>102908</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>130761</t>
+          <t>128790</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175527</t>
+          <t>173321</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>206910</t>
+          <t>207852</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268136</t>
+          <t>263629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>397971</t>
+          <t>398943</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>441934</t>
+          <t>442326</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>468288</t>
+          <t>468087</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>521821</t>
+          <t>518656</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>880739</t>
+          <t>879058</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>949389</t>
+          <t>946857</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2016</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,97 +7585,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>20,14%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7079</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6426</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>20628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54793</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65576</t>
+          <t>65792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34304</t>
+          <t>34401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82821</t>
+          <t>82989</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97999</t>
+          <t>98268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>39081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49770</t>
+          <t>49383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>49553</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63042</t>
+          <t>62782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>15457</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>29059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96710</t>
+          <t>96715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111114</t>
+          <t>111378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26801</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127990</t>
+          <t>128600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147922</t>
+          <t>148201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27589</t>
+          <t>27289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32605</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36986</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>34773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61522</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>151895</t>
+          <t>153150</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>174514</t>
+          <t>173654</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>56270</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77270</t>
+          <t>77675</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>217146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>246563</t>
+          <t>247007</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>22449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18250</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>38945</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27534</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50429</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53465</t>
+          <t>53727</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>82839</t>
+          <t>83664</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90293</t>
+          <t>89597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111777</t>
+          <t>111915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99948</t>
+          <t>98363</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124627</t>
+          <t>123672</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196620</t>
+          <t>195398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>229569</t>
+          <t>228383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21181</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21181</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77071</t>
+          <t>77344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115420</t>
+          <t>114547</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77071</t>
+          <t>77344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115420</t>
+          <t>114547</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>263097</t>
+          <t>264156</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>304734</t>
+          <t>305487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>263097</t>
+          <t>264156</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>304734</t>
+          <t>305487</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58937</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36590</t>
+          <t>36783</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65586</t>
+          <t>66871</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78082</t>
+          <t>77486</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114791</t>
+          <t>116091</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>81906</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>154962</t>
+          <t>157124</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>208990</t>
+          <t>208389</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>220785</t>
+          <t>220977</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>279684</t>
+          <t>283147</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>461198</t>
+          <t>460230</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>495858</t>
+          <t>496806</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>512202</t>
+          <t>511635</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>568464</t>
+          <t>567251</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>984549</t>
+          <t>978232</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1052531</t>
+          <t>1051886</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2023</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,47 +11174,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>18468</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>12693</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>25317</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>10,68%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>24,45%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>18468</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>12918</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>25357</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91363</t>
+          <t>91012</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101384</t>
+          <t>100640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46526</t>
+          <t>47118</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56981</t>
+          <t>57055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141578</t>
+          <t>140935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>155598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26711</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74704</t>
+          <t>75113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86412</t>
+          <t>86006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38330</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108441</t>
+          <t>107946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122253</t>
+          <t>122154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77209</t>
+          <t>76759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89495</t>
+          <t>89053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>29468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39297</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109969</t>
+          <t>110309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125984</t>
+          <t>125826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31944</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38831</t>
+          <t>39015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62387</t>
+          <t>61721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49042</t>
+          <t>50051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59903</t>
+          <t>60273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101281</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162075</t>
+          <t>162429</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>184865</t>
+          <t>183906</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>231675</t>
+          <t>231073</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>318804</t>
+          <t>318127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>404738</t>
+          <t>404851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>531521</t>
+          <t>530379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37837</t>
+          <t>37612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46974</t>
+          <t>47506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39738</t>
+          <t>39903</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56060</t>
+          <t>56041</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>52750</t>
+          <t>53287</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>72186</t>
+          <t>72600</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61058</t>
+          <t>60023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73843</t>
+          <t>73541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117781</t>
+          <t>117661</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136473</t>
+          <t>136998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184083</t>
+          <t>184206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206684</t>
+          <t>205338</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37357</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56003</t>
+          <t>56038</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38100</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57533</t>
+          <t>57676</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67242</t>
+          <t>67898</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88867</t>
+          <t>89388</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68076</t>
+          <t>68002</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90413</t>
+          <t>90838</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>183977</t>
+          <t>184831</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>208362</t>
+          <t>209687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>185746</t>
+          <t>185028</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>210921</t>
+          <t>210447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,78%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38407</t>
+          <t>39154</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59715</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48488</t>
+          <t>53006</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>128053</t>
+          <t>125727</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>98561</t>
+          <t>92131</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>173179</t>
+          <t>174571</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71018</t>
+          <t>70593</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>97954</t>
+          <t>98404</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>94516</t>
+          <t>93106</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>234512</t>
+          <t>234047</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>172590</t>
+          <t>168639</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>311752</t>
+          <t>310546</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>487287</t>
+          <t>488509</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>519949</t>
+          <t>520011</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>660898</t>
+          <t>661437</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>872730</t>
+          <t>871256</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1174946</t>
+          <t>1176984</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1381410</t>
+          <t>1388610</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5401-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5401-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>41147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>53863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72871</t>
+          <t>73051</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,63%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>47121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46450</t>
+          <t>45722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>25380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48515</t>
+          <t>49084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62600</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65427</t>
+          <t>65146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81485</t>
+          <t>81388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29489</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14877</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32969</t>
+          <t>32441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34265</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58468</t>
+          <t>57759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50467</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>77106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181209</t>
+          <t>180847</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>207744</t>
+          <t>207139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56520</t>
+          <t>56396</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71416</t>
+          <t>71719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>242565</t>
+          <t>245667</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>272475</t>
+          <t>274939</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16755</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>21982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>32337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>36192</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47736</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53231</t>
+          <t>53186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72936</t>
+          <t>72453</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>94016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116653</t>
+          <t>117099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41214</t>
+          <t>41952</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18962</t>
+          <t>20243</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41879</t>
+          <t>41997</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82265</t>
+          <t>81615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118878</t>
+          <t>119479</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82820</t>
+          <t>83360</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>119431</t>
+          <t>119446</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>277456</t>
+          <t>275903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>314384</t>
+          <t>314997</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278544</t>
+          <t>276908</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>318549</t>
+          <t>317537</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39864</t>
+          <t>40266</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>37059</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62961</t>
+          <t>61695</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97896</t>
+          <t>95798</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>69257</t>
+          <t>69185</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104762</t>
+          <t>102386</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136953</t>
+          <t>136621</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>182362</t>
+          <t>180706</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>216944</t>
+          <t>217996</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268954</t>
+          <t>273017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>365623</t>
+          <t>368238</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>403986</t>
+          <t>405735</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>442243</t>
+          <t>444283</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>492768</t>
+          <t>493120</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>825963</t>
+          <t>824603</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>885411</t>
+          <t>885478</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30304</t>
+          <t>29018</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>16931</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50384</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17472</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43381</t>
+          <t>42552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56409</t>
+          <t>56286</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50614</t>
+          <t>51669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68870</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>28703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40160</t>
+          <t>41038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82771</t>
+          <t>82392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102946</t>
+          <t>103286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44152</t>
+          <t>44173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118838</t>
+          <t>117462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142970</t>
+          <t>143207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40990</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48268</t>
+          <t>46694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25305</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40148</t>
+          <t>39044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66386</t>
+          <t>66959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153401</t>
+          <t>151516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181538</t>
+          <t>180770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32060</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47006</t>
+          <t>46426</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189238</t>
+          <t>190024</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>221440</t>
+          <t>222180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20557</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41040</t>
+          <t>41253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31672</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57819</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27431</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33858</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55736</t>
+          <t>57886</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>49790</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77521</t>
+          <t>79663</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61565</t>
+          <t>61647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79980</t>
+          <t>80115</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100520</t>
+          <t>98702</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126823</t>
+          <t>126964</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>165873</t>
+          <t>168466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>200323</t>
+          <t>202458</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36850</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64682</t>
+          <t>66218</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65362</t>
+          <t>65051</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58481</t>
+          <t>58808</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92096</t>
+          <t>88566</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61700</t>
+          <t>59865</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91899</t>
+          <t>90575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>249215</t>
+          <t>249702</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>288731</t>
+          <t>287431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>253125</t>
+          <t>252328</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>290692</t>
+          <t>289584</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70021</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>78748</t>
+          <t>75864</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>115536</t>
+          <t>115266</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127310</t>
+          <t>127454</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>178482</t>
+          <t>176998</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66302</t>
+          <t>66315</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>102908</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128790</t>
+          <t>130250</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>173321</t>
+          <t>174334</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>207852</t>
+          <t>206657</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>263629</t>
+          <t>263919</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>397822</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>442326</t>
+          <t>443466</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>468087</t>
+          <t>469690</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>518656</t>
+          <t>522247</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>879058</t>
+          <t>882857</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>946857</t>
+          <t>951081</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>55187</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65792</t>
+          <t>65388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34401</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82989</t>
+          <t>83387</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>98451</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39081</t>
+          <t>39453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49383</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49553</t>
+          <t>50528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62782</t>
+          <t>63408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>14656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96715</t>
+          <t>97126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111378</t>
+          <t>110439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26843</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40256</t>
+          <t>41059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128600</t>
+          <t>128172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148201</t>
+          <t>147050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>33131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29798</t>
+          <t>30469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>18075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>39305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34773</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61893</t>
+          <t>60313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153150</t>
+          <t>153619</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>173654</t>
+          <t>174806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56270</t>
+          <t>55651</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77675</t>
+          <t>77044</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>217146</t>
+          <t>217968</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>247007</t>
+          <t>247783</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36159</t>
+          <t>36538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38945</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>51107</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53727</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83664</t>
+          <t>82394</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89597</t>
+          <t>90336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111915</t>
+          <t>111521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98363</t>
+          <t>99862</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123672</t>
+          <t>123190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>195398</t>
+          <t>196903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228383</t>
+          <t>230197</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48519</t>
+          <t>47651</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48519</t>
+          <t>47651</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77344</t>
+          <t>77712</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114547</t>
+          <t>115638</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77344</t>
+          <t>77712</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114547</t>
+          <t>115638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>264156</t>
+          <t>263674</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>305487</t>
+          <t>304628</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>264156</t>
+          <t>263674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>305487</t>
+          <t>304628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59064</t>
+          <t>58111</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36783</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>66871</t>
+          <t>68375</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>77486</t>
+          <t>77758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>116091</t>
+          <t>117894</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52557</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>81906</t>
+          <t>82250</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>157124</t>
+          <t>156742</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>208389</t>
+          <t>206110</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>220977</t>
+          <t>219825</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>283147</t>
+          <t>281984</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>460230</t>
+          <t>460615</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>496806</t>
+          <t>496080</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>511635</t>
+          <t>513562</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>567251</t>
+          <t>567867</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>978232</t>
+          <t>983623</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1051886</t>
+          <t>1052592</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>17181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25317</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96731</t>
+          <t>109011</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91012</t>
+          <t>102551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100640</t>
+          <t>113109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52520</t>
+          <t>60695</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47118</t>
+          <t>54207</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57055</t>
+          <t>65396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>149250</t>
+          <t>169706</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140935</t>
+          <t>161499</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155598</t>
+          <t>176399</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,102 +11462,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>7294</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3740</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>12014</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5250</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>7087</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3747</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>11913</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -11575,17 +11575,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>30048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81339</t>
+          <t>90165</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75113</t>
+          <t>83061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86006</t>
+          <t>95313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34203</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>34675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>45223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115543</t>
+          <t>131090</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107946</t>
+          <t>122340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122154</t>
+          <t>137625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10047</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>38290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>83664</t>
+          <t>92704</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76759</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89053</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>31843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>42844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>118295</t>
+          <t>129882</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110309</t>
+          <t>120609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125826</t>
+          <t>138623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154292</t>
+          <t>169873</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154292</t>
+          <t>169873</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154292</t>
+          <t>169873</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>26111</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37017</t>
+          <t>40266</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61721</t>
+          <t>51152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>41892</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>53353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60273</t>
+          <t>28872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>60542</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20326</t>
+          <t>53988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99801</t>
+          <t>77004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -12600,102 +12600,102 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>173813</t>
+          <t>191350</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162429</t>
+          <t>179411</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183906</t>
+          <t>202405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>73,78%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>69,18%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>78,04%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>94131</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>86865</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>101054</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>66,37%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>77,21%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>285481</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>270544</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>298833</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>73,16%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>68,36%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>77,4%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>292913</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>231073</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>318127</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>70,73%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>466726</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>404851</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>530379</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>82,71%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>32415</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23394</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>40906</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>39218</t>
+          <t>41714</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47506</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47957</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39903</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56041</t>
+          <t>61177</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>62076</t>
+          <t>68352</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53287</t>
+          <t>57926</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>72600</t>
+          <t>80121</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>67966</t>
+          <t>74485</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60023</t>
+          <t>67009</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73541</t>
+          <t>81450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>127163</t>
+          <t>135675</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117661</t>
+          <t>126019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136998</t>
+          <t>146379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>195128</t>
+          <t>210160</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184206</t>
+          <t>196750</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>205338</t>
+          <t>222041</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>91290</t>
+          <t>99983</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91290</t>
+          <t>99983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91290</t>
+          <t>99983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>296423</t>
+          <t>320227</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296423</t>
+          <t>320227</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296423</t>
+          <t>320227</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46129</t>
+          <t>50072</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38192</t>
+          <t>39725</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56038</t>
+          <t>62397</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>47140</t>
+          <t>51097</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57676</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>78362</t>
+          <t>83893</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67898</t>
+          <t>71488</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89388</t>
+          <t>96347</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>79496</t>
+          <t>85072</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68002</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90838</t>
+          <t>97412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,67 +13547,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>197181</t>
+          <t>211818</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>184831</t>
+          <t>197074</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>209687</t>
+          <t>225523</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>65,22%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>212890</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>200577</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>227307</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>60,99%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>57,46%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>65,19%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>198240</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>185028</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>210447</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>61,02%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>56,95%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>48056</t>
+          <t>50157</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39154</t>
+          <t>39624</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59528</t>
+          <t>61397</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>97277</t>
+          <t>105651</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53006</t>
+          <t>92156</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>125727</t>
+          <t>120473</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>145333</t>
+          <t>155808</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>92131</t>
+          <t>137873</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>176606</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>84105</t>
+          <t>91255</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>70593</t>
+          <t>77047</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>98404</t>
+          <t>108040</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>182085</t>
+          <t>198180</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>180262</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>234047</t>
+          <t>219814</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>266190</t>
+          <t>289435</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>168639</t>
+          <t>266319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>310546</t>
+          <t>313311</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>504571</t>
+          <t>558788</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>488509</t>
+          <t>540362</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>520011</t>
+          <t>575400</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>738612</t>
+          <t>580421</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>661437</t>
+          <t>558430</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>871256</t>
+          <t>600059</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1243183</t>
+          <t>1139209</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1176984</t>
+          <t>1111512</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1388610</t>
+          <t>1169123</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>636732</t>
+          <t>700200</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>636732</t>
+          <t>700200</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>636732</t>
+          <t>700200</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1017974</t>
+          <t>884252</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1017974</t>
+          <t>884252</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1017974</t>
+          <t>884252</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1654706</t>
+          <t>1584452</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1654706</t>
+          <t>1584452</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1654706</t>
+          <t>1584452</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
